--- a/Planilha_de_HQs.xlsx
+++ b/Planilha_de_HQs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guilh\OneDrive\Documentos\GitHub\EstanteDoLeitor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B121375-FBD4-4B9E-9ACD-D92BCBC2E334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F7C004-BCB1-4E7C-B0F6-683B6B3EFD6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1018,12 +1018,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1053,12 +1059,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1407,25 +1414,26 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>5</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I2" t="s">
@@ -1433,25 +1441,26 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I3" t="s">
@@ -1459,25 +1468,26 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
         <v>5</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I4" t="s">
@@ -1485,45 +1495,48 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
         <v>3</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>6</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>6</v>
       </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>2</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>4</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J6" t="s">
@@ -1531,48 +1544,50 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E7">
-        <v>16</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="E7" s="3">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J8" t="s">
@@ -1580,94 +1595,98 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <v>5</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="3">
         <v>5</v>
       </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
         <v>9</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="3">
         <v>9</v>
       </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="G11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>11</v>
-      </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3">
+        <v>11</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="J12" t="s">
@@ -1675,25 +1694,26 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="E13">
-        <v>16</v>
-      </c>
-      <c r="F13">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="E13" s="3">
+        <v>16</v>
+      </c>
+      <c r="F13" s="3">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>18</v>
       </c>
     </row>
